--- a/planilhas/LISTA DE PROCESSO PG POWERADE MOD 1.xlsx
+++ b/planilhas/LISTA DE PROCESSO PG POWERADE MOD 1.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Plan1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -341,7 +341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -608,6 +608,34 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PG POWERADE MOD 1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Solda Mig</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ESTRUTURA TUBULAR CORPO LARGO</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>98</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>002027</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/planilhas/LISTA DE PROCESSO PG POWERADE MOD 1.xlsx
+++ b/planilhas/LISTA DE PROCESSO PG POWERADE MOD 1.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Plan1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -341,7 +341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -636,6 +636,314 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PG POWERADE MOD 1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Solda Mig</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ESTRUTURA TUBULAR CORPO ESTREITO</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>98</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>002028</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PG POWERADE MOD 1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Solda Mig</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ARAMADO CORPO LARGO</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>98</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>002029</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PG POWERADE MOD 1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Solda Mig</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ARAMADO CORPO ESTREITO</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>98</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>002030</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PG POWERADE MOD 1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Solda Mig</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BDJS NO CORPO LARGO</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>98</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>002031</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PG POWERADE MOD 1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Solda Mig</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BDJS NO CORPO ESTREITO</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>98</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>002032</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PG POWERADE MOD 1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Solda Mig</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CHAPA FREEZER CORPO LARGO</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>98</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>002033</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PG POWERADE MOD 1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Solda Mig</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CHAPA FREEZER CORPO ESTREITO</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>98</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>002034</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PG POWERADE MOD 1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Solda Mig</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MOLDURA NO CORPO LARGO</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>98</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>002035</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PG POWERADE MOD 1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Solda Mig</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MOLDURA NO CORPO ESTREITO</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>98</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>002036</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PG POWERADE MOD 1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Solda Mig</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PARACHOQUE</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>98</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>002037</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PG POWERADE MOD 1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Solda Mig</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TESTEIRA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>98</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>002038</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
